--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488043_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488043_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9508</v>
+        <v>5.3611</v>
       </c>
       <c r="E2" t="n">
         <v>6.6709</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7201</v>
+        <v>-1.3098</v>
       </c>
       <c r="G2" t="n">
         <v>2.8331</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5229</v>
+        <v>0.9333</v>
       </c>
       <c r="T2" t="n">
         <v>0.8629</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6601</v>
+        <v>0.0704</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4669</v>
+        <v>3.7829</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3218</v>
+        <v>2.5255</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1451</v>
+        <v>1.2574</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3647</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5889</v>
+        <v>0.9049</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6757</v>
+        <v>0.8794</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0868</v>
+        <v>0.0255</v>
       </c>
       <c r="V3" t="n">
         <v>5.432</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1133</v>
+        <v>2.4528</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1133</v>
+        <v>3.593</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.1402</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1133</v>
+        <v>0.6161</v>
       </c>
       <c r="H4" t="n">
-        <v>0.908</v>
+        <v>-2.7397</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2053</v>
+        <v>3.3557</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1133</v>
+        <v>2.9372</v>
       </c>
       <c r="K4" t="n">
-        <v>0.908</v>
+        <v>-1.6067</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2053</v>
+        <v>4.544</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2.3212</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.1329</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.3892</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1899</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1107</v>
+        <v>2.2046</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1107</v>
+        <v>2.9203</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.7157</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1107</v>
+        <v>0.8423</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3027</v>
+        <v>-0.5945</v>
       </c>
       <c r="I5" t="n">
-        <v>1.808</v>
+        <v>1.4368</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1107</v>
+        <v>2.956</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3027</v>
+        <v>0.3367</v>
       </c>
       <c r="L5" t="n">
-        <v>1.808</v>
+        <v>2.6193</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.1137</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.9312</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1825</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.6378</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.0357</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.6734</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1093</v>
+        <v>2.1133</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2072</v>
+        <v>2.1133</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.098</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8423</v>
+        <v>2.1133</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5945</v>
+        <v>0.908</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4368</v>
+        <v>1.2053</v>
       </c>
       <c r="J6" t="n">
-        <v>2.956</v>
+        <v>2.1133</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3367</v>
+        <v>0.908</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6193</v>
+        <v>1.2053</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1137</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9312</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1825</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5424</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7488</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2912</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6098</v>
+        <v>2.1107</v>
       </c>
       <c r="E7" t="n">
-        <v>2.778</v>
+        <v>2.1107</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1683</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6161</v>
+        <v>2.1107</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7397</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3557</v>
+        <v>1.808</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9372</v>
+        <v>2.1107</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6067</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>4.544</v>
+        <v>1.808</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3212</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1329</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1882</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.264</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4257</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1618</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3529</v>
+        <v>0.3225</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6545</v>
+        <v>-0.1975</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3016</v>
+        <v>0.52</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3988</v>
+        <v>-1.5141</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4237</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0249</v>
+        <v>-2.2002</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3732</v>
+        <v>-1.0888</v>
       </c>
       <c r="K8" t="n">
-        <v>1.285</v>
+        <v>0.8682</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0881</v>
+        <v>-1.957</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.4253</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8613</v>
+        <v>-0.1822</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.113</v>
+        <v>-0.2431</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9541</v>
+        <v>0.8544</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2636</v>
+        <v>0.8913</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3095</v>
+        <v>-0.0369</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1479</v>
+        <v>0.1561</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.7792</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6324</v>
+        <v>-0.6231</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5141</v>
+        <v>-1.1563</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6860000000000001</v>
+        <v>-1.317</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2002</v>
+        <v>0.1607</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0888</v>
+        <v>0.2936</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8682</v>
+        <v>-0.5177</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.957</v>
+        <v>0.8113</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4253</v>
+        <v>-1.4499</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1822</v>
+        <v>-0.7993</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2431</v>
+        <v>-0.6506</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6798</v>
+        <v>0.7177</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6044</v>
+        <v>0.4856</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.2321</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4689</v>
+        <v>-0.386</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2885</v>
+        <v>0.719</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8197</v>
+        <v>-1.1051</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1563</v>
+        <v>0.3988</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.317</v>
+        <v>0.4237</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1607</v>
+        <v>-0.0249</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2936</v>
+        <v>1.3732</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5177</v>
+        <v>1.285</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8113</v>
+        <v>0.0881</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4499</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7993</v>
+        <v>-0.8613</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6506</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0305</v>
+        <v>1.2151</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9949</v>
+        <v>1.3281</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0355</v>
+        <v>-0.113</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5985</v>
+        <v>-3.0963</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0108</v>
+        <v>-3.7052</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4123</v>
+        <v>0.6089</v>
       </c>
       <c r="G11" t="n">
         <v>0.4222</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0562</v>
+        <v>0.446</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1872</v>
+        <v>0.1184</v>
       </c>
       <c r="U11" t="n">
-        <v>0.131</v>
+        <v>0.3276</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4542</v>
+        <v>-4.0716</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2056</v>
+        <v>-4.1037</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2486</v>
+        <v>0.0322</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7739</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0552</v>
+        <v>0.4378</v>
       </c>
       <c r="T12" t="n">
-        <v>0.727</v>
+        <v>0.8289</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.3911</v>
       </c>
       <c r="V12" t="n">
         <v>0.4627</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4193</v>
+        <v>-6.0917</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.743</v>
+        <v>-3.7243</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6763</v>
+        <v>-2.3675</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5827</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6295</v>
+        <v>-0.3019</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8736</v>
+        <v>0.1451</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7559</v>
+        <v>-0.447</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.858499999999999</v>
+        <v>4.858400000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>9.701099999999999</v>
+        <v>9.7012</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.8428</v>
+        <v>-4.8429</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.055199999999999</v>
+        <v>-4.0552</v>
       </c>
       <c r="H14" t="n">
         <v>-3.3761</v>
@@ -1519,19 +1519,19 @@
         <v>-0.6792999999999996</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9803</v>
+        <v>6.980300000000003</v>
       </c>
       <c r="K14" t="n">
         <v>1.8609</v>
       </c>
       <c r="L14" t="n">
-        <v>5.119499999999998</v>
+        <v>5.119499999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-11.0354</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.236999999999999</v>
+        <v>-5.237</v>
       </c>
       <c r="O14" t="n">
         <v>-5.7985</v>
@@ -1546,13 +1546,13 @@
         <v>11.8933</v>
       </c>
       <c r="S14" t="n">
-        <v>6.424100000000001</v>
+        <v>6.4242</v>
       </c>
       <c r="T14" t="n">
         <v>5.893200000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5308999999999999</v>
+        <v>0.5308999999999997</v>
       </c>
       <c r="V14" t="n">
         <v>3.4805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5145</v>
+        <v>2.3238</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9652</v>
+        <v>3.8633</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4507</v>
+        <v>-1.5395</v>
       </c>
       <c r="G15" t="n">
         <v>0.5583</v>
@@ -1624,13 +1624,13 @@
         <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2136</v>
+        <v>0.0229</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5692</v>
+        <v>0.4673</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3556</v>
+        <v>-0.4444</v>
       </c>
       <c r="V15" t="n">
         <v>0.5532</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VEGA MERAYO</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7607</v>
+        <v>2.2858</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2346</v>
+        <v>1.848</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.474</v>
+        <v>0.4378</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4153</v>
+        <v>1.1985</v>
       </c>
       <c r="H16" t="n">
-        <v>0.097</v>
+        <v>-0.309</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3184</v>
+        <v>1.5076</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6367</v>
+        <v>1.0862</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3961</v>
+        <v>0.5523</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0328</v>
+        <v>0.534</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2214</v>
+        <v>0.1123</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4931</v>
+        <v>-0.8613</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7144</v>
+        <v>0.9736</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5088</v>
+        <v>-1.5684</v>
       </c>
       <c r="T16" t="n">
-        <v>0.382</v>
+        <v>-0.5404</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8907</v>
+        <v>-1.028</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4577</v>
+        <v>2.6556</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>3.2843</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7494</v>
+        <v>-0.6287</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>J. VEGA MERAYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4774</v>
+        <v>2.0088</v>
       </c>
       <c r="E17" t="n">
-        <v>2.654</v>
+        <v>3.2346</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1766</v>
+        <v>-1.2258</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6531</v>
+        <v>1.4153</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3745</v>
+        <v>0.097</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7214</v>
+        <v>1.3184</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1561</v>
+        <v>2.6367</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9553</v>
+        <v>-0.3961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2009</v>
+        <v>3.0328</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.503</v>
+        <v>-1.2214</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4193</v>
+        <v>0.4931</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9223</v>
+        <v>-1.7144</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4456</v>
+        <v>-0.2606</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4979</v>
+        <v>0.382</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0523</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8107</v>
+        <v>0.4577</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8107</v>
+        <v>-0.7494</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4395</v>
+        <v>1.2053</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3386</v>
+        <v>1.2053</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1009</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1985</v>
+        <v>1.2053</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.309</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5076</v>
+        <v>1.2053</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0862</v>
+        <v>1.2053</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5523</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.534</v>
+        <v>1.2053</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1123</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8613</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9736</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.4147</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0497</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3649</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6556</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2843</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2053</v>
+        <v>0.5044</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2053</v>
+        <v>1.7372</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.2328</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2053</v>
+        <v>0.6531</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.3745</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2053</v>
+        <v>-0.7214</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2053</v>
+        <v>1.1561</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.9553</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2053</v>
+        <v>0.2009</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.503</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.4193</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.9223</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.4726</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.1084</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2402</v>
+        <v>-0.7925</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0925</v>
+        <v>-1.7481</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1477</v>
+        <v>0.9556</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0304</v>
+        <v>-0.04</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4439</v>
+        <v>-0.0915</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4744</v>
+        <v>0.0516</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4614</v>
+        <v>-0.2688</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4174</v>
+        <v>0.3701</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0441</v>
+        <v>-0.639</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.431</v>
+        <v>0.2289</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8613</v>
+        <v>-0.4617</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4303</v>
+        <v>0.6905</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.9508</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5581</v>
+        <v>-0.4881</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4756</v>
+        <v>-0.4626</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7925</v>
+        <v>-0.9919</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7481</v>
+        <v>-0.7038</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9556</v>
+        <v>-0.2881</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.04</v>
+        <v>0.0304</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0915</v>
+        <v>-0.4439</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0516</v>
+        <v>0.4744</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2688</v>
+        <v>0.4614</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3701</v>
+        <v>0.4174</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.639</v>
+        <v>0.0441</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2289</v>
+        <v>-0.431</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4617</v>
+        <v>-0.8613</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6905</v>
+        <v>0.4303</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1982</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9508</v>
+        <v>-0.669</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4881</v>
+        <v>-0.0531</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4626</v>
+        <v>-0.616</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6287</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.37</v>
+        <v>-1.0657</v>
       </c>
       <c r="E22" t="n">
         <v>0.5273</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8973</v>
+        <v>-1.593</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1884</v>
@@ -2170,13 +2170,13 @@
         <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3979</v>
+        <v>-0.0936</v>
       </c>
       <c r="T22" t="n">
         <v>0.2644</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6623</v>
+        <v>-0.358</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3873</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2586</v>
+        <v>-2.4656</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9076</v>
+        <v>-2.8057</v>
       </c>
       <c r="F23" t="n">
-        <v>0.649</v>
+        <v>0.3402</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9355</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8044</v>
+        <v>-1.0114</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8001</v>
+        <v>-0.6983</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0042</v>
+        <v>-0.3131</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3027</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6727</v>
+        <v>-2.8029</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5493</v>
+        <v>-2.0399</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1234</v>
+        <v>-0.763</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1248</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2378</v>
+        <v>-0.368</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4771</v>
+        <v>0.0322</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7607</v>
+        <v>-0.4002</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1207</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9218</v>
+        <v>-4.3889</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.2755</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.137</v>
+        <v>-4.1135</v>
       </c>
       <c r="G25" t="n">
         <v>2.2828</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8516</v>
+        <v>-1.3188</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9873</v>
+        <v>-0.478</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8643</v>
+        <v>-0.8408</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7672</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.8584</v>
+        <v>-4.179399999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>4.842699999999998</v>
+        <v>4.8427</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.7012</v>
+        <v>-9.022099999999998</v>
       </c>
       <c r="G26" t="n">
         <v>4.055</v>
@@ -2452,7 +2452,7 @@
         <v>3.3762</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6793000000000001</v>
+        <v>0.6792999999999997</v>
       </c>
       <c r="J26" t="n">
         <v>11.0354</v>
@@ -2461,7 +2461,7 @@
         <v>5.237</v>
       </c>
       <c r="L26" t="n">
-        <v>5.798599999999999</v>
+        <v>5.7986</v>
       </c>
       <c r="M26" t="n">
         <v>-6.980199999999999</v>
@@ -2470,10 +2470,10 @@
         <v>-1.8608</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.1194</v>
+        <v>-5.119400000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9910000000000003</v>
+        <v>0.9909999999999994</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.8932</v>
@@ -2482,13 +2482,13 @@
         <v>12.8845</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.424200000000001</v>
+        <v>-5.745100000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5309</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.8932</v>
+        <v>-5.214099999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-3.4807</v>
@@ -2497,7 +2497,7 @@
         <v>6.231700000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.712200000000001</v>
+        <v>-9.712199999999999</v>
       </c>
     </row>
   </sheetData>
